--- a/data/trans_orig/P1422-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2012</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425788</t>
+          <t>426426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308867</t>
+          <t>309258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739413</t>
+          <t>739934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750693</t>
+          <t>750717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,47 +1110,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414524</t>
+          <t>412562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>751614</t>
+          <t>751601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23322</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612588</t>
+          <t>611878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626167</t>
+          <t>625548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251249</t>
+          <t>251377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866222</t>
+          <t>867466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883362</t>
+          <t>883591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>27928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>31616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1131654</t>
+          <t>1131081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1149663</t>
+          <t>1149247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>753369</t>
+          <t>754376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>762736</t>
+          <t>762765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1891896</t>
+          <t>1892115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910412</t>
+          <t>1910768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499535</t>
+          <t>499055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508627</t>
+          <t>508610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>747740</t>
+          <t>748263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>758155</t>
+          <t>758166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1251417</t>
+          <t>1250916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1265437</t>
+          <t>1265202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18365</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1090986</t>
+          <t>1089839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1104205</t>
+          <t>1104157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1358331</t>
+          <t>1357563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1371166</t>
+          <t>1371079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>49499</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44159</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75169</t>
+          <t>76092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3374610</t>
+          <t>3372411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3399273</t>
+          <t>3398797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3510179</t>
+          <t>3509854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3530891</t>
+          <t>3530185</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6893656</t>
+          <t>6892733</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6924666</t>
+          <t>6923858</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2016</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413872</t>
+          <t>414067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426095</t>
+          <t>425493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332655</t>
+          <t>335125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345848</t>
+          <t>345855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>753837</t>
+          <t>752266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770139</t>
+          <t>770035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,62 +3745,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7548</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2143</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7063</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370688</t>
+          <t>369752</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742437</t>
+          <t>741952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513975</t>
+          <t>512953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521128</t>
+          <t>521132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157560</t>
+          <t>157838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676133</t>
+          <t>675883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685972</t>
+          <t>685985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138338</t>
+          <t>1139097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147826</t>
+          <t>1147825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>818180</t>
+          <t>817505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1961568</t>
+          <t>1960684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972653</t>
+          <t>1972537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612151</t>
+          <t>612099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619899</t>
+          <t>619903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725400</t>
+          <t>725363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736089</t>
+          <t>736096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1341404</t>
+          <t>1341458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1353961</t>
+          <t>1354237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281980</t>
+          <t>281834</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1068613</t>
+          <t>1069351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1080828</t>
+          <t>1080939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1354895</t>
+          <t>1354665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1367063</t>
+          <t>1367149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31457</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32734</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58218</t>
+          <t>58653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3354265</t>
+          <t>3354030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3372180</t>
+          <t>3372491</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3498862</t>
+          <t>3499247</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3519264</t>
+          <t>3519723</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6859100</t>
+          <t>6858665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6886481</t>
+          <t>6886082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2023</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>493585</t>
+          <t>493800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503134</t>
+          <t>503264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441561</t>
+          <t>442104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446837</t>
+          <t>446851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>939762</t>
+          <t>939171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>949129</t>
+          <t>949024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>438428</t>
+          <t>438668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448240</t>
+          <t>447982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>375469</t>
+          <t>375791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380765</t>
+          <t>380759</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>817101</t>
+          <t>816633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827520</t>
+          <t>827761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645229</t>
+          <t>644711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664594</t>
+          <t>663932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161528</t>
+          <t>160943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166215</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810883</t>
+          <t>810881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829933</t>
+          <t>829905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1015486</t>
+          <t>1015308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026880</t>
+          <t>1026768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968096</t>
+          <t>968153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>975973</t>
+          <t>975862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1986645</t>
+          <t>1986832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2001838</t>
+          <t>2001195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,47 +7389,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8738</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5322</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13875</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8738</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>13621</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462727</t>
+          <t>463250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471046</t>
+          <t>470963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,49 +7502,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>829467</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>824330</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>832883</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>829467</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>824584</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>833201</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1803</t>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1291402</t>
+          <t>1290979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1302527</t>
+          <t>1302796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19702</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236464</t>
+          <t>234715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>740990</t>
+          <t>741531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>752644</t>
+          <t>753146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>980249</t>
+          <t>981044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>992582</t>
+          <t>992993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>30298</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54742</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,82 +8075,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>34205</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>25195</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>44736</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>75810</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>62034</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>92351</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>34205</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>25362</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>44591</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>75810</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>59841</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>91418</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3317854</t>
+          <t>3317320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3342474</t>
+          <t>3342298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,82 +8188,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5173</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3539076</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3528545</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3548086</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6870066</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6853525</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6883842</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>99,11%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3539076</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3528690</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3547919</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>8410</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6870066</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6854458</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6886035</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1422-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>12821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426426</t>
+          <t>424507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309258</t>
+          <t>309213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739934</t>
+          <t>738844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750717</t>
+          <t>750591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412562</t>
+          <t>413684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>751601</t>
+          <t>750957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611878</t>
+          <t>612470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625548</t>
+          <t>625462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251377</t>
+          <t>252188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259088</t>
+          <t>259090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867466</t>
+          <t>866170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883591</t>
+          <t>883541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1131081</t>
+          <t>1132777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1149247</t>
+          <t>1149821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>754376</t>
+          <t>753602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>762765</t>
+          <t>762759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892115</t>
+          <t>1891288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910768</t>
+          <t>1910827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499055</t>
+          <t>497341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508610</t>
+          <t>508522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>748263</t>
+          <t>747121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>758166</t>
+          <t>758126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1250916</t>
+          <t>1251702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1265202</t>
+          <t>1265208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1089839</t>
+          <t>1090620</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1104157</t>
+          <t>1104172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1357563</t>
+          <t>1357237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1371079</t>
+          <t>1371093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>23714</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49499</t>
+          <t>49400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>38655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44967</t>
+          <t>43643</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>76845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3372411</t>
+          <t>3372510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3398797</t>
+          <t>3398196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3509854</t>
+          <t>3508260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3530185</t>
+          <t>3529434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6892733</t>
+          <t>6891980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6923858</t>
+          <t>6925182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414067</t>
+          <t>412984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425493</t>
+          <t>425510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335125</t>
+          <t>334069</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345855</t>
+          <t>345859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>752266</t>
+          <t>755159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770035</t>
+          <t>770078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369752</t>
+          <t>369682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741952</t>
+          <t>741944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512953</t>
+          <t>513491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521132</t>
+          <t>521135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>156042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675883</t>
+          <t>675628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685985</t>
+          <t>685984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1139097</t>
+          <t>1138016</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147825</t>
+          <t>1147769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>817505</t>
+          <t>816663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1960684</t>
+          <t>1961944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972537</t>
+          <t>1972975</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612099</t>
+          <t>611795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619903</t>
+          <t>619724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725363</t>
+          <t>725296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736096</t>
+          <t>736079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1341458</t>
+          <t>1341906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1354237</t>
+          <t>1354226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281834</t>
+          <t>282355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1069351</t>
+          <t>1068829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1080939</t>
+          <t>1080827</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1354665</t>
+          <t>1355730</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1367149</t>
+          <t>1367049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32349</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31236</t>
+          <t>30525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3354030</t>
+          <t>3352838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3372491</t>
+          <t>3371744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3499247</t>
+          <t>3498670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3519723</t>
+          <t>3519323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6858665</t>
+          <t>6858381</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6886082</t>
+          <t>6886793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,17 +6032,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500246</t>
+          <t>544136</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>493800</t>
+          <t>537147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503264</t>
+          <t>547984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,17 +6145,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>445101</t>
+          <t>485834</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>442104</t>
+          <t>482121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446851</t>
+          <t>487768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>945347</t>
+          <t>1029970</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>939171</t>
+          <t>1022124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>949024</t>
+          <t>1034281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,22 +6375,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>444534</t>
+          <t>475264</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>438668</t>
+          <t>468809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447982</t>
+          <t>479222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,27 +6488,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>378958</t>
+          <t>419417</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>375791</t>
+          <t>415706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380759</t>
+          <t>421229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>823492</t>
+          <t>894681</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816633</t>
+          <t>887539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827761</t>
+          <t>899074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451329</t>
+          <t>482290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451329</t>
+          <t>482290</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451329</t>
+          <t>482290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833240</t>
+          <t>904782</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833240</t>
+          <t>904782</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833240</t>
+          <t>904782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22834</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>24066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>656000</t>
+          <t>458644</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644711</t>
+          <t>451198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663932</t>
+          <t>464321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164604</t>
+          <t>184429</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160943</t>
+          <t>180052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>186395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>820604</t>
+          <t>643074</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810881</t>
+          <t>634175</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829905</t>
+          <t>648504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1022285</t>
+          <t>1118544</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1015308</t>
+          <t>1111810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026768</t>
+          <t>1123282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>972724</t>
+          <t>855539</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968153</t>
+          <t>850636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>975862</t>
+          <t>858123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1995009</t>
+          <t>1974084</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1986832</t>
+          <t>1965321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2001195</t>
+          <t>1979681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033953</t>
+          <t>1130916</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033953</t>
+          <t>1130916</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033953</t>
+          <t>1130916</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012047</t>
+          <t>1992128</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012047</t>
+          <t>1992128</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012047</t>
+          <t>1992128</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>23406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>468122</t>
+          <t>560828</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463250</t>
+          <t>555231</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470963</t>
+          <t>563894</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>829467</t>
+          <t>818751</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>824330</t>
+          <t>813086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>832883</t>
+          <t>822469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1297589</t>
+          <t>1379579</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1290979</t>
+          <t>1372320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1302796</t>
+          <t>1384815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838205</t>
+          <t>828750</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838205</t>
+          <t>828750</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838205</t>
+          <t>828750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312254</t>
+          <t>1395726</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312254</t>
+          <t>1395726</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312254</t>
+          <t>1395726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>711</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,17 +7782,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -7825,27 +7825,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239802</t>
+          <t>236517</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234715</t>
+          <t>233311</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>748222</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>741531</t>
+          <t>822633</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>753146</t>
+          <t>835134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,17 +7895,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>988025</t>
+          <t>1066523</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>981044</t>
+          <t>1058586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>992993</t>
+          <t>1071920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>32850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34205</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44736</t>
+          <t>49073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>75810</t>
+          <t>82819</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62034</t>
+          <t>67300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92351</t>
+          <t>98266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3330990</t>
+          <t>3393934</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3317320</t>
+          <t>3379379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3342298</t>
+          <t>3405922</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3539076</t>
+          <t>3593976</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3528545</t>
+          <t>3582884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3548086</t>
+          <t>3602014</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6870066</t>
+          <t>6987909</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6853525</t>
+          <t>6972462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6883842</t>
+          <t>7003428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3372596</t>
+          <t>3438772</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3372596</t>
+          <t>3438772</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3372596</t>
+          <t>3438772</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573281</t>
+          <t>3631957</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573281</t>
+          <t>3631957</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573281</t>
+          <t>3631957</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6945876</t>
+          <t>7070728</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6945876</t>
+          <t>7070728</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6945876</t>
+          <t>7070728</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
